--- a/ツール/【原本_個人】企業名_インボイス枠_個人2026.xlsx
+++ b/ツール/【原本_個人】企業名_インボイス枠_個人2026.xlsx
@@ -55560,7 +55560,7 @@
       </c>
       <c r="F11" s="331"/>
       <c r="H11" s="332" t="str">
-        <f>H1/(B5+B6+B7)</f>
+        <f>H10/(B5+B6+B7)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J11" s="312" t="s">
